--- a/output/pdf_financials_xlsx/SPMC.xlsx
+++ b/output/pdf_financials_xlsx/SPMC.xlsx
@@ -3233,16 +3233,16 @@
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.284</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.701656</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.335773</v>
       </c>
     </row>
     <row r="93">
@@ -5435,7 +5435,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -6634,7 +6638,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -7242,7 +7250,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SPMC.xlsx
+++ b/output/pdf_financials_xlsx/SPMC.xlsx
@@ -691,7 +691,7 @@
         <v>0.019327</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.234</v>
+        <v>1.39</v>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.199</v>
+        <v>1.388</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>1.164399</v>
@@ -721,7 +721,7 @@
         <v>-0.019327</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.234</v>
+        <v>-1.39</v>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.199</v>
+        <v>-1.388</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>-1.164399</v>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.070169</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.20106</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.070169</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.20106</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -15850,7 +15850,7 @@
         </is>
       </c>
       <c r="G221" s="5" t="n">
-        <v>-1.39</v>
+        <v>1.39</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -15858,10 +15858,10 @@
         </is>
       </c>
       <c r="I221" s="5" t="n">
-        <v>-1.388</v>
+        <v>1.388</v>
       </c>
       <c r="J221" s="5" t="n">
-        <v>-1.164</v>
+        <v>1.164</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SPMC.xlsx
+++ b/output/pdf_financials_xlsx/SPMC.xlsx
@@ -2472,7 +2472,7 @@
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.048692</v>
       </c>
     </row>
     <row r="68">
